--- a/base/StructureDefinition-SGLogicalModel.xlsx
+++ b/base/StructureDefinition-SGLogicalModel.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -365,7 +365,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -765,7 +765,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -827,7 +827,7 @@
     <t>Codes for the meaning of the defined structure (SNOMED CT and LOINC codes, as an example).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-use</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-use|4.0.1</t>
   </si>
   <si>
     <t>keywords</t>
@@ -1060,7 +1060,7 @@
     <t>Either a resource or a data type, including logical model types.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/defined-types</t>
+    <t>http://hl7.org/fhir/ValueSet/defined-types|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">sdf-11
@@ -1070,7 +1070,7 @@
     <t>StructureDefinition.baseDefinition</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1)
 </t>
   </si>
   <si>
@@ -1310,7 +1310,7 @@
     <t>Codes that indicate the meaning of a data element.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">pattern:system}
@@ -2133,7 +2133,7 @@
     <t>StructureDefinition.differential.element.type.profile</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureDefinition|ImplementationGuide)
+    <t xml:space="preserve">canonical(StructureDefinition|4.0.1|ImplementationGuide|4.0.1)
 </t>
   </si>
   <si>
@@ -2720,7 +2720,7 @@
     <t>StructureDefinition.differential.element.binding.valueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -3150,15 +3150,15 @@
   <dimension ref="A1:AO212"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="65.15234375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="64.44140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.94921875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.1171875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="56.4296875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="11" max="11" width="255.0" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
@@ -3169,27 +3169,27 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="94.92578125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="57.40234375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="43.8046875" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="40.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="83.734375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="49.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="38.69921875" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="35.42578125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="115.46875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="26.71875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="101.75390625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="235.45703125" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10914,7 +10914,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" hidden="true">
+    <row r="67">
       <c r="A67" t="s" s="2">
         <v>419</v>
       </c>
@@ -11856,7 +11856,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75" hidden="true">
+    <row r="75">
       <c r="A75" t="s" s="2">
         <v>463</v>
       </c>
@@ -12798,7 +12798,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" hidden="true">
+    <row r="83">
       <c r="A83" t="s" s="2">
         <v>473</v>
       </c>
@@ -13740,7 +13740,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
         <v>483</v>
       </c>
@@ -14682,7 +14682,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="99" hidden="true">
+    <row r="99">
       <c r="A99" t="s" s="2">
         <v>493</v>
       </c>
@@ -15624,7 +15624,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107" hidden="true">
+    <row r="107">
       <c r="A107" t="s" s="2">
         <v>503</v>
       </c>
@@ -16566,7 +16566,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" hidden="true">
+    <row r="115">
       <c r="A115" t="s" s="2">
         <v>513</v>
       </c>
@@ -17508,7 +17508,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123" hidden="true">
+    <row r="123">
       <c r="A123" t="s" s="2">
         <v>523</v>
       </c>
@@ -18450,7 +18450,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131" hidden="true">
+    <row r="131">
       <c r="A131" t="s" s="2">
         <v>533</v>
       </c>
@@ -28032,12 +28032,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AO212">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
